--- a/xlsx/Power/p24.xlsx
+++ b/xlsx/Power/p24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57F541B-2144-46ED-8386-28BBD55A8E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D6D1AC-6A2C-40F9-875F-AEF1FA3BF4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E40FD697-00AA-44BF-91AC-C2370FEB74E6}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E40FD697-00AA-44BF-91AC-C2370FEB74E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="C1">
-        <v>0.33800000000000002</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="D1">
-        <v>0.45800000000000002</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="E1">
-        <v>0.57299999999999995</v>
+        <v>0.27900000000000003</v>
       </c>
       <c r="F1">
-        <v>0.623</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="G1">
-        <v>0.71399999999999997</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="H1">
-        <v>0.747</v>
+        <v>0.60699999999999998</v>
       </c>
       <c r="I1">
-        <v>0.82</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="J1">
-        <v>0.86499999999999999</v>
+        <v>0.77700000000000002</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="C2">
-        <v>0.35499999999999998</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="D2">
-        <v>0.47599999999999998</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="E2">
-        <v>0.57699999999999996</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="F2">
-        <v>0.63</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="G2">
-        <v>0.72099999999999997</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="H2">
-        <v>0.752</v>
+        <v>0.627</v>
       </c>
       <c r="I2">
-        <v>0.82799999999999996</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="J2">
-        <v>0.86199999999999999</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.22</v>
       </c>
       <c r="C3">
-        <v>0.29299999999999998</v>
+        <v>0.33</v>
       </c>
       <c r="D3">
-        <v>0.39600000000000002</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="E3">
-        <v>0.51500000000000001</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="F3">
-        <v>0.56599999999999995</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="G3">
-        <v>0.64900000000000002</v>
+        <v>0.65</v>
       </c>
       <c r="H3">
-        <v>0.71</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="I3">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="J3">
-        <v>0.81299999999999994</v>
+        <v>0.81599999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.11600000000000001</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="B4">
-        <v>0.20100000000000001</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="C4">
-        <v>0.27100000000000002</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="D4">
-        <v>0.36199999999999999</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="E4">
-        <v>0.46500000000000002</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="F4">
-        <v>0.52</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="G4">
         <v>0.60199999999999998</v>
       </c>
       <c r="H4">
-        <v>0.63900000000000001</v>
+        <v>0.63800000000000001</v>
       </c>
       <c r="I4">
-        <v>0.69499999999999995</v>
+        <v>0.69399999999999995</v>
       </c>
       <c r="J4">
-        <v>0.75700000000000001</v>
+        <v>0.76100000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.114</v>
       </c>
       <c r="C5">
-        <v>0.14499999999999999</v>
+        <v>1E-3</v>
       </c>
       <c r="D5">
-        <v>0.16400000000000001</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E5">
-        <v>0.218</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="F5">
-        <v>0.22600000000000001</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="G5">
-        <v>0.28199999999999997</v>
+        <v>0.127</v>
       </c>
       <c r="H5">
-        <v>0.28000000000000003</v>
+        <v>0.153</v>
       </c>
       <c r="I5">
-        <v>0.32400000000000001</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="J5">
-        <v>0.373</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.248</v>
       </c>
       <c r="C6">
-        <v>0.34100000000000003</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="D6">
-        <v>0.441</v>
+        <v>0.505</v>
       </c>
       <c r="E6">
-        <v>0.53400000000000003</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="F6">
-        <v>0.60599999999999998</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="G6">
-        <v>0.69</v>
+        <v>0.69899999999999995</v>
       </c>
       <c r="H6">
-        <v>0.747</v>
+        <v>0.755</v>
       </c>
       <c r="I6">
-        <v>0.82699999999999996</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="J6">
-        <v>0.84299999999999997</v>
+        <v>0.85499999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="C7">
-        <v>0.31</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="D7">
-        <v>0.40600000000000003</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="E7">
-        <v>0.48399999999999999</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="F7">
-        <v>0.57299999999999995</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="G7">
-        <v>0.66100000000000003</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="H7">
         <v>0.71799999999999997</v>
       </c>
       <c r="I7">
-        <v>0.79500000000000004</v>
+        <v>0.79200000000000004</v>
       </c>
       <c r="J7">
-        <v>0.82</v>
+        <v>0.81699999999999995</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.121</v>
       </c>
       <c r="C8">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.221</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E8">
-        <v>0.26500000000000001</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="F8">
-        <v>0.311</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="G8">
-        <v>0.374</v>
+        <v>0.18</v>
       </c>
       <c r="H8">
-        <v>0.40100000000000002</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="I8">
-        <v>0.499</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="J8">
-        <v>0.55200000000000005</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="C9">
-        <v>0.13100000000000001</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="D9">
-        <v>0.11600000000000001</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="E9">
-        <v>0.16500000000000001</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="F9">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="G9">
-        <v>0.24</v>
+        <v>0.311</v>
       </c>
       <c r="H9">
-        <v>0.25800000000000001</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="I9">
-        <v>0.33</v>
+        <v>0.34799999999999998</v>
       </c>
       <c r="J9">
-        <v>0.377</v>
+        <v>0.39500000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p24.xlsx
+++ b/xlsx/Power/p24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D6D1AC-6A2C-40F9-875F-AEF1FA3BF4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD582C93-CF12-4CAB-8661-AC6D423C1CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E40FD697-00AA-44BF-91AC-C2370FEB74E6}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E40FD697-00AA-44BF-91AC-C2370FEB74E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="C1">
-        <v>3.3000000000000002E-2</v>
+        <v>0.33800000000000002</v>
       </c>
       <c r="D1">
-        <v>0.13500000000000001</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="E1">
-        <v>0.27900000000000003</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="F1">
-        <v>0.40899999999999997</v>
+        <v>0.623</v>
       </c>
       <c r="G1">
-        <v>0.53500000000000003</v>
+        <v>0.71399999999999997</v>
       </c>
       <c r="H1">
-        <v>0.60699999999999998</v>
+        <v>0.747</v>
       </c>
       <c r="I1">
-        <v>0.69799999999999995</v>
+        <v>0.82</v>
       </c>
       <c r="J1">
-        <v>0.77700000000000002</v>
+        <v>0.86499999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.25900000000000001</v>
       </c>
       <c r="C2">
-        <v>3.4000000000000002E-2</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="D2">
-        <v>0.13800000000000001</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="E2">
-        <v>0.28599999999999998</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="F2">
-        <v>0.41899999999999998</v>
+        <v>0.63</v>
       </c>
       <c r="G2">
-        <v>0.55500000000000005</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="H2">
-        <v>0.627</v>
+        <v>0.752</v>
       </c>
       <c r="I2">
-        <v>0.70699999999999996</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="J2">
-        <v>0.78</v>
+        <v>0.86199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.22</v>
       </c>
       <c r="C3">
-        <v>0.33</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="D3">
-        <v>0.41199999999999998</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="E3">
-        <v>0.52100000000000002</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="F3">
-        <v>0.56699999999999995</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="G3">
-        <v>0.65</v>
+        <v>0.64900000000000002</v>
       </c>
       <c r="H3">
-        <v>0.71099999999999997</v>
+        <v>0.71</v>
       </c>
       <c r="I3">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="J3">
-        <v>0.81599999999999995</v>
+        <v>0.81299999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.13200000000000001</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="B4">
-        <v>0.21199999999999999</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="C4">
-        <v>0.27500000000000002</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="D4">
-        <v>0.35699999999999998</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="E4">
-        <v>0.46600000000000003</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="F4">
-        <v>0.52400000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="G4">
         <v>0.60199999999999998</v>
       </c>
       <c r="H4">
-        <v>0.63800000000000001</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="I4">
-        <v>0.69399999999999995</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="J4">
-        <v>0.76100000000000001</v>
+        <v>0.75700000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.114</v>
       </c>
       <c r="C5">
-        <v>1E-3</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="D5">
-        <v>1.4E-2</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="E5">
-        <v>4.9000000000000002E-2</v>
+        <v>0.218</v>
       </c>
       <c r="F5">
-        <v>7.6999999999999999E-2</v>
+        <v>0.22600000000000001</v>
       </c>
       <c r="G5">
-        <v>0.127</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="H5">
-        <v>0.153</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I5">
-        <v>0.16700000000000001</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="J5">
-        <v>0.224</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.248</v>
       </c>
       <c r="C6">
-        <v>0.50800000000000001</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="D6">
-        <v>0.505</v>
+        <v>0.44</v>
       </c>
       <c r="E6">
-        <v>0.58299999999999996</v>
+        <v>0.53400000000000003</v>
       </c>
       <c r="F6">
-        <v>0.63700000000000001</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="G6">
-        <v>0.69899999999999995</v>
+        <v>0.69</v>
       </c>
       <c r="H6">
-        <v>0.755</v>
+        <v>0.747</v>
       </c>
       <c r="I6">
-        <v>0.83599999999999997</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="J6">
-        <v>0.85499999999999998</v>
+        <v>0.84299999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="C7">
-        <v>0.29899999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="D7">
-        <v>0.40500000000000003</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="E7">
-        <v>0.48699999999999999</v>
+        <v>0.48399999999999999</v>
       </c>
       <c r="F7">
-        <v>0.56599999999999995</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="G7">
-        <v>0.65500000000000003</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="H7">
         <v>0.71799999999999997</v>
       </c>
       <c r="I7">
-        <v>0.79200000000000004</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="J7">
-        <v>0.81699999999999995</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.121</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="D8">
-        <v>1.6E-2</v>
+        <v>0.221</v>
       </c>
       <c r="E8">
-        <v>5.3999999999999999E-2</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="F8">
-        <v>0.13700000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="G8">
-        <v>0.18</v>
+        <v>0.374</v>
       </c>
       <c r="H8">
-        <v>0.24299999999999999</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="I8">
-        <v>0.10299999999999999</v>
+        <v>0.499</v>
       </c>
       <c r="J8">
-        <v>0.12</v>
+        <v>0.55200000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="C9">
-        <v>0.44900000000000001</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="D9">
-        <v>0.88500000000000001</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="E9">
-        <v>0.68200000000000005</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="F9">
+        <v>0.19</v>
+      </c>
+      <c r="G9">
+        <v>0.24</v>
+      </c>
+      <c r="H9">
+        <v>0.25800000000000001</v>
+      </c>
+      <c r="I9">
         <v>0.33</v>
       </c>
-      <c r="G9">
-        <v>0.311</v>
-      </c>
-      <c r="H9">
-        <v>0.30499999999999999</v>
-      </c>
-      <c r="I9">
-        <v>0.34799999999999998</v>
-      </c>
       <c r="J9">
-        <v>0.39500000000000002</v>
+        <v>0.377</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p24.xlsx
+++ b/xlsx/Power/p24.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD582C93-CF12-4CAB-8661-AC6D423C1CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C875F14-0F11-46D0-86FE-AA70B790ABD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E40FD697-00AA-44BF-91AC-C2370FEB74E6}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{E40FD697-00AA-44BF-91AC-C2370FEB74E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="B1">
-        <v>0.25600000000000001</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="C1">
-        <v>0.33800000000000002</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="D1">
-        <v>0.45800000000000002</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="E1">
-        <v>0.57299999999999995</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="F1">
         <v>0.623</v>
@@ -419,196 +419,196 @@
         <v>0.71399999999999997</v>
       </c>
       <c r="H1">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="I1">
-        <v>0.82</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="J1">
-        <v>0.86499999999999999</v>
+        <v>0.86599999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.13400000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="B2">
-        <v>0.25900000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="C2">
         <v>0.35499999999999998</v>
       </c>
       <c r="D2">
-        <v>0.47599999999999998</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="E2">
-        <v>0.57699999999999996</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="F2">
-        <v>0.63</v>
+        <v>0.628</v>
       </c>
       <c r="G2">
-        <v>0.72099999999999997</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="H2">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="I2">
         <v>0.82799999999999996</v>
       </c>
       <c r="J2">
-        <v>0.86199999999999999</v>
+        <v>0.86499999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.11899999999999999</v>
+        <v>0.11799999999999999</v>
       </c>
       <c r="B3">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="C3">
-        <v>0.29299999999999998</v>
+        <v>0.29699999999999999</v>
       </c>
       <c r="D3">
         <v>0.39600000000000002</v>
       </c>
       <c r="E3">
-        <v>0.51500000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="F3">
         <v>0.56599999999999995</v>
       </c>
       <c r="G3">
-        <v>0.64900000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="H3">
-        <v>0.71</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="I3">
-        <v>0.754</v>
+        <v>0.76</v>
       </c>
       <c r="J3">
-        <v>0.81299999999999994</v>
+        <v>0.81899999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.11600000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="B4">
-        <v>0.20100000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="C4">
-        <v>0.27100000000000002</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="D4">
-        <v>0.36199999999999999</v>
+        <v>0.36299999999999999</v>
       </c>
       <c r="E4">
-        <v>0.46500000000000002</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="F4">
-        <v>0.52</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="G4">
-        <v>0.60199999999999998</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="H4">
-        <v>0.63900000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="I4">
-        <v>0.69499999999999995</v>
+        <v>0.70299999999999996</v>
       </c>
       <c r="J4">
-        <v>0.75700000000000001</v>
+        <v>0.76400000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>9.9000000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.114</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>0.14499999999999999</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>0.16400000000000001</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="E5">
-        <v>0.218</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="F5">
-        <v>0.22600000000000001</v>
+        <v>2.3E-2</v>
       </c>
       <c r="G5">
-        <v>0.28199999999999997</v>
+        <v>0.03</v>
       </c>
       <c r="H5">
-        <v>0.28000000000000003</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="I5">
-        <v>0.32400000000000001</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="J5">
-        <v>0.372</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.13</v>
+        <v>0.129</v>
       </c>
       <c r="B6">
         <v>0.248</v>
       </c>
       <c r="C6">
-        <v>0.34100000000000003</v>
+        <v>0.34</v>
       </c>
       <c r="D6">
-        <v>0.44</v>
+        <v>0.438</v>
       </c>
       <c r="E6">
-        <v>0.53400000000000003</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="F6">
-        <v>0.60599999999999998</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="G6">
-        <v>0.69</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="H6">
-        <v>0.747</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="I6">
-        <v>0.82699999999999996</v>
+        <v>0.82299999999999995</v>
       </c>
       <c r="J6">
-        <v>0.84299999999999997</v>
+        <v>0.84799999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.129</v>
+        <v>0.127</v>
       </c>
       <c r="B7">
-        <v>0.22800000000000001</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="C7">
-        <v>0.31</v>
+        <v>0.30499999999999999</v>
       </c>
       <c r="D7">
-        <v>0.40600000000000003</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="E7">
         <v>0.48399999999999999</v>
       </c>
       <c r="F7">
-        <v>0.57299999999999995</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="G7">
-        <v>0.66100000000000003</v>
+        <v>0.65900000000000003</v>
       </c>
       <c r="H7">
         <v>0.71799999999999997</v>
@@ -625,19 +625,19 @@
         <v>0.08</v>
       </c>
       <c r="B8">
-        <v>0.121</v>
+        <v>0.123</v>
       </c>
       <c r="C8">
         <v>0.161</v>
       </c>
       <c r="D8">
-        <v>0.221</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="E8">
-        <v>0.26500000000000001</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="F8">
-        <v>0.311</v>
+        <v>0.313</v>
       </c>
       <c r="G8">
         <v>0.374</v>
@@ -646,10 +646,10 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="I8">
-        <v>0.499</v>
+        <v>0.5</v>
       </c>
       <c r="J8">
-        <v>0.55200000000000005</v>
+        <v>0.55400000000000005</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -657,31 +657,31 @@
         <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.13500000000000001</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="C9">
-        <v>0.13100000000000001</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="D9">
         <v>0.11600000000000001</v>
       </c>
       <c r="E9">
-        <v>0.16500000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="F9">
-        <v>0.19</v>
+        <v>0.193</v>
       </c>
       <c r="G9">
-        <v>0.24</v>
+        <v>0.23799999999999999</v>
       </c>
       <c r="H9">
-        <v>0.25800000000000001</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="I9">
-        <v>0.33</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="J9">
-        <v>0.377</v>
+        <v>0.38100000000000001</v>
       </c>
     </row>
   </sheetData>
